--- a/templates_excel/template_instructor.xlsx
+++ b/templates_excel/template_instructor.xlsx
@@ -232,7 +232,7 @@
     <numFmt numFmtId="178" formatCode="\(#&quot;시&quot;&quot;간&quot;\)"/>
     <numFmt numFmtId="179" formatCode="\(&quot;이&quot;&quot;번&quot;&quot;차&quot;&quot;수&quot;&quot;:&quot;\ #.#\)"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -320,8 +320,16 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -348,6 +356,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -571,7 +584,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -716,6 +729,10 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="8" xfId="6" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -5498,7 +5515,7 @@
     </row>
     <row r="73" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="24">
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B4:F4"/>
@@ -5513,9 +5530,6 @@
     <mergeCell ref="E62:I62"/>
     <mergeCell ref="E63:I63"/>
     <mergeCell ref="E64:I64"/>
-    <mergeCell ref="D61:D64"/>
-    <mergeCell ref="D65:D68"/>
-    <mergeCell ref="D69:D72"/>
     <mergeCell ref="B69:C72"/>
     <mergeCell ref="E69:I69"/>
     <mergeCell ref="E70:I70"/>
